--- a/output/pdf_financials_xlsx/CAU.H.xlsx
+++ b/output/pdf_financials_xlsx/CAU.H.xlsx
@@ -947,7 +947,7 @@
         <v>0.060953</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01509</v>
+        <v>0.521554</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.024365</v>
@@ -1072,49 +1072,49 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00911</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006535</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007841000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006581</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003769</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003376</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004442</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007722</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011067</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.004285</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000348</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.011037</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.02867</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.028893</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.016436</v>
       </c>
     </row>
     <row r="13">
@@ -2141,49 +2141,49 @@
         <v>-0.530577</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.630834</v>
+        <v>-4.639944</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.072265</v>
+        <v>-0.0788</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.061372</v>
+        <v>-0.069213</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.057451</v>
+        <v>-0.06403200000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.024402</v>
+        <v>-0.028171</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.041428</v>
+        <v>-0.044804</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.017405</v>
+        <v>-0.021847</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.01778</v>
+        <v>-0.025502</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.014948</v>
+        <v>-0.026015</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.023772</v>
+        <v>-0.028057</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.028224</v>
+        <v>-0.028572</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.020806</v>
+        <v>-0.031843</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.001391</v>
+        <v>-0.027279</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.000848</v>
+        <v>-0.029741</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.09452199999999999</v>
+        <v>-0.110958</v>
       </c>
     </row>
     <row r="28">
@@ -2263,49 +2263,49 @@
         <v>-0.527132</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.628438</v>
+        <v>-4.637548</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.072265</v>
+        <v>-0.0788</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.061372</v>
+        <v>-0.069213</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.057451</v>
+        <v>-0.06403200000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.024402</v>
+        <v>-0.028171</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.041428</v>
+        <v>-0.044804</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.017405</v>
+        <v>-0.021847</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.01778</v>
+        <v>-0.025502</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.014948</v>
+        <v>-0.026015</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.023772</v>
+        <v>-0.028057</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.028224</v>
+        <v>-0.028572</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.020806</v>
+        <v>-0.031843</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.001391</v>
+        <v>-0.027279</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.000848</v>
+        <v>-0.029741</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.09452199999999999</v>
+        <v>-0.110958</v>
       </c>
     </row>
     <row r="30">
@@ -2330,46 +2330,46 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-50806.12513721186</v>
+        <v>-50906.12513721186</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1105.814843152257</v>
+        <v>-1205.814843152257</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-782.7062874633338</v>
+        <v>-882.7062874633338</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-872.9828293572405</v>
+        <v>-972.9828293572405</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-647.4396391615813</v>
+        <v>-747.4396391615813</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1227.132701421801</v>
+        <v>-1327.132701421801</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-391.8280054029717</v>
+        <v>-491.8280054029716</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-230.2512302512303</v>
+        <v>-330.2512302512303</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-135.0682208367218</v>
+        <v>-235.0682208367218</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-554.7724620770128</v>
+        <v>-654.7724620770128</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-8110.344827586207</v>
+        <v>-8210.344827586207</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-188.5113708435263</v>
+        <v>-288.5113708435263</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>4.851761423090338</v>
+        <v>-95.14823857690966</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-2.934966947011387</v>
+        <v>-102.9349669470114</v>
       </c>
       <c r="S30" s="1" t="inlineStr">
         <is>
@@ -2563,16 +2563,16 @@
         <v>0.015175</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.014688</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.013843</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.003907</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.002953</v>
       </c>
     </row>
     <row r="35">
@@ -2685,16 +2685,16 @@
         <v>0.65001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.6166160000000001</v>
+        <v>0.631304</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.620877</v>
+        <v>0.63472</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.62834</v>
+        <v>0.632247</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.595014</v>
+        <v>0.597967</v>
       </c>
     </row>
     <row r="37">
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.014688</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.013843</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.003907</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.002953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -27678,7 +27678,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAU.H.xlsx
+++ b/output/pdf_financials_xlsx/CAU.H.xlsx
@@ -7402,10 +7402,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000426</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001859</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000426</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001859</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8978,10 +8978,10 @@
         <v>-0.118083</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.250121</v>
+        <v>-0.250547</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.41798</v>
+        <v>-0.419839</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -21430,7 +21430,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
